--- a/templates/invoice_template_direct_v2.xlsx
+++ b/templates/invoice_template_direct_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Проекты\Агент Авто Континент\01_БОТ_АКТУАЛЬНЫЙ\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8D60C9-7929-41EC-9DC1-3D6B69D7354A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCA286D-37F7-49CF-91D0-53D4D8ECD626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -628,17 +628,214 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -656,203 +853,6 @@
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -883,7 +883,7 @@
     <xdr:ext cx="1768048" cy="1544504"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr descr="stamp" id="4" name="image2.png" title="Изображение">
+        <xdr:cNvPr id="4" name="image2.png" descr="stamp" title="Изображение">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F869081-3D0B-42FB-8CAB-9AEA07D8FD90}"/>
@@ -914,14 +914,14 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>152401</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>67733</xdr:rowOff>
+      <xdr:colOff>25401</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1205130" cy="607695"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr descr="signature" id="5" name="image1.png" title="Изображение">
+        <xdr:cNvPr id="5" name="image1.png" descr="signature" title="Изображение">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C2EBBCE-23F2-4BEB-ABFD-12E548EB3FF5}"/>
@@ -938,7 +938,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2125134" y="5452533"/>
+          <a:off x="1998134" y="5710766"/>
           <a:ext cx="1205130" cy="607695"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1216,435 +1216,435 @@
     </row>
     <row r="2" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8"/>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="49" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="52" t="s">
+      <c r="P2" s="58"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="53"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="53"/>
-      <c r="AB2" s="54"/>
-      <c r="AC2" s="55"/>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="55"/>
-      <c r="AF2" s="55"/>
-      <c r="AG2" s="55"/>
-      <c r="AH2" s="55"/>
-      <c r="AI2" s="55"/>
-      <c r="AJ2" s="55"/>
-      <c r="AK2" s="55"/>
-      <c r="AL2" s="56"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
+      <c r="W2" s="33"/>
+      <c r="X2" s="33"/>
+      <c r="Y2" s="33"/>
+      <c r="Z2" s="33"/>
+      <c r="AA2" s="33"/>
+      <c r="AB2" s="34"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="14"/>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="15"/>
     </row>
     <row r="3" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
-      <c r="M3" s="58"/>
-      <c r="N3" s="59"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="56"/>
       <c r="O3" s="60"/>
-      <c r="P3" s="61"/>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="64"/>
-      <c r="Y3" s="64"/>
-      <c r="Z3" s="64"/>
-      <c r="AA3" s="64"/>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="66"/>
-      <c r="AD3" s="67" t="s">
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="28"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="AE3" s="67"/>
-      <c r="AF3" s="67"/>
-      <c r="AG3" s="67"/>
-      <c r="AH3" s="67"/>
-      <c r="AI3" s="67"/>
-      <c r="AJ3" s="67"/>
-      <c r="AK3" s="66"/>
-      <c r="AL3" s="68"/>
+      <c r="AE3" s="47"/>
+      <c r="AF3" s="47"/>
+      <c r="AG3" s="47"/>
+      <c r="AH3" s="47"/>
+      <c r="AI3" s="47"/>
+      <c r="AJ3" s="47"/>
+      <c r="AK3" s="16"/>
+      <c r="AL3" s="17"/>
     </row>
     <row r="4" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="59"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="56"/>
       <c r="O4" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="61"/>
-      <c r="R4" s="62"/>
-      <c r="S4" s="63" t="s">
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="64"/>
-      <c r="Y4" s="64"/>
-      <c r="Z4" s="64"/>
-      <c r="AA4" s="64"/>
-      <c r="AB4" s="65"/>
-      <c r="AC4" s="69"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="67"/>
-      <c r="AG4" s="67"/>
-      <c r="AH4" s="67"/>
-      <c r="AI4" s="67"/>
-      <c r="AJ4" s="67"/>
-      <c r="AK4" s="69"/>
-      <c r="AL4" s="70"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="18"/>
+      <c r="AD4" s="47"/>
+      <c r="AE4" s="47"/>
+      <c r="AF4" s="47"/>
+      <c r="AG4" s="47"/>
+      <c r="AH4" s="47"/>
+      <c r="AI4" s="47"/>
+      <c r="AJ4" s="47"/>
+      <c r="AK4" s="18"/>
+      <c r="AL4" s="19"/>
     </row>
     <row r="5" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="58"/>
-      <c r="N5" s="59"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="56"/>
       <c r="O5" s="60"/>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="62"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="64"/>
-      <c r="U5" s="64"/>
-      <c r="V5" s="64"/>
-      <c r="W5" s="64"/>
-      <c r="X5" s="64"/>
-      <c r="Y5" s="64"/>
-      <c r="Z5" s="64"/>
-      <c r="AA5" s="64"/>
-      <c r="AB5" s="65"/>
-      <c r="AC5" s="71"/>
-      <c r="AD5" s="67"/>
-      <c r="AE5" s="67"/>
-      <c r="AF5" s="67"/>
-      <c r="AG5" s="67"/>
-      <c r="AH5" s="67"/>
-      <c r="AI5" s="67"/>
-      <c r="AJ5" s="67"/>
-      <c r="AK5" s="71"/>
-      <c r="AL5" s="72"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="44"/>
+      <c r="S5" s="26"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="47"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="47"/>
+      <c r="AJ5" s="47"/>
+      <c r="AK5" s="20"/>
+      <c r="AL5" s="21"/>
     </row>
     <row r="6" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="73" t="s">
+      <c r="B6" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="75"/>
-      <c r="O6" s="76"/>
-      <c r="P6" s="77"/>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="79"/>
-      <c r="T6" s="80"/>
-      <c r="U6" s="80"/>
-      <c r="V6" s="80"/>
-      <c r="W6" s="80"/>
-      <c r="X6" s="80"/>
-      <c r="Y6" s="80"/>
-      <c r="Z6" s="80"/>
-      <c r="AA6" s="80"/>
-      <c r="AB6" s="81"/>
-      <c r="AC6" s="71"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="67"/>
-      <c r="AG6" s="67"/>
-      <c r="AH6" s="67"/>
-      <c r="AI6" s="67"/>
-      <c r="AJ6" s="67"/>
-      <c r="AK6" s="71"/>
-      <c r="AL6" s="82"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="50"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="46"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="31"/>
+      <c r="AC6" s="20"/>
+      <c r="AD6" s="47"/>
+      <c r="AE6" s="47"/>
+      <c r="AF6" s="47"/>
+      <c r="AG6" s="47"/>
+      <c r="AH6" s="47"/>
+      <c r="AI6" s="47"/>
+      <c r="AJ6" s="47"/>
+      <c r="AK6" s="20"/>
+      <c r="AL6" s="22"/>
     </row>
     <row r="7" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="84"/>
-      <c r="D7" s="67" t="s">
+      <c r="C7" s="24"/>
+      <c r="D7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="85" t="s">
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="85"/>
-      <c r="K7" s="86" t="s">
+      <c r="J7" s="80"/>
+      <c r="K7" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="L7" s="86"/>
-      <c r="M7" s="86"/>
-      <c r="N7" s="87"/>
-      <c r="O7" s="61" t="s">
+      <c r="L7" s="90"/>
+      <c r="M7" s="90"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="61"/>
-      <c r="Q7" s="61"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="64" t="s">
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="T7" s="64"/>
-      <c r="U7" s="64"/>
-      <c r="V7" s="64"/>
-      <c r="W7" s="64"/>
-      <c r="X7" s="64"/>
-      <c r="Y7" s="64"/>
-      <c r="Z7" s="64"/>
-      <c r="AA7" s="64"/>
-      <c r="AB7" s="65"/>
-      <c r="AC7" s="88"/>
-      <c r="AD7" s="67"/>
-      <c r="AE7" s="67"/>
-      <c r="AF7" s="67"/>
-      <c r="AG7" s="67"/>
-      <c r="AH7" s="67"/>
-      <c r="AI7" s="67"/>
-      <c r="AJ7" s="67"/>
-      <c r="AK7" s="71"/>
-      <c r="AL7" s="82"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="27"/>
+      <c r="V7" s="27"/>
+      <c r="W7" s="27"/>
+      <c r="X7" s="27"/>
+      <c r="Y7" s="27"/>
+      <c r="Z7" s="27"/>
+      <c r="AA7" s="27"/>
+      <c r="AB7" s="28"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="47"/>
+      <c r="AE7" s="47"/>
+      <c r="AF7" s="47"/>
+      <c r="AG7" s="47"/>
+      <c r="AH7" s="47"/>
+      <c r="AI7" s="47"/>
+      <c r="AJ7" s="47"/>
+      <c r="AK7" s="20"/>
+      <c r="AL7" s="22"/>
     </row>
     <row r="8" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="89" t="s">
+      <c r="B8" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="90"/>
-      <c r="D8" s="90"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="90"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="90"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="90"/>
-      <c r="N8" s="91"/>
-      <c r="O8" s="61"/>
-      <c r="P8" s="61"/>
-      <c r="Q8" s="61"/>
-      <c r="R8" s="62"/>
-      <c r="S8" s="64"/>
-      <c r="T8" s="64"/>
-      <c r="U8" s="64"/>
-      <c r="V8" s="64"/>
-      <c r="W8" s="64"/>
-      <c r="X8" s="64"/>
-      <c r="Y8" s="64"/>
-      <c r="Z8" s="64"/>
-      <c r="AA8" s="64"/>
-      <c r="AB8" s="65"/>
-      <c r="AC8" s="88"/>
-      <c r="AD8" s="67"/>
-      <c r="AE8" s="67"/>
-      <c r="AF8" s="67"/>
-      <c r="AG8" s="67"/>
-      <c r="AH8" s="67"/>
-      <c r="AI8" s="67"/>
-      <c r="AJ8" s="67"/>
-      <c r="AK8" s="71"/>
-      <c r="AL8" s="82"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="44"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="27"/>
+      <c r="V8" s="27"/>
+      <c r="W8" s="27"/>
+      <c r="X8" s="27"/>
+      <c r="Y8" s="27"/>
+      <c r="Z8" s="27"/>
+      <c r="AA8" s="27"/>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="47"/>
+      <c r="AE8" s="47"/>
+      <c r="AF8" s="47"/>
+      <c r="AG8" s="47"/>
+      <c r="AH8" s="47"/>
+      <c r="AI8" s="47"/>
+      <c r="AJ8" s="47"/>
+      <c r="AK8" s="20"/>
+      <c r="AL8" s="22"/>
     </row>
     <row r="9" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="89"/>
-      <c r="C9" s="90"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="90"/>
-      <c r="J9" s="90"/>
-      <c r="K9" s="90"/>
-      <c r="L9" s="90"/>
-      <c r="M9" s="90"/>
-      <c r="N9" s="91"/>
-      <c r="O9" s="61"/>
-      <c r="P9" s="61"/>
-      <c r="Q9" s="61"/>
-      <c r="R9" s="62"/>
-      <c r="S9" s="64"/>
-      <c r="T9" s="64"/>
-      <c r="U9" s="64"/>
-      <c r="V9" s="64"/>
-      <c r="W9" s="64"/>
-      <c r="X9" s="64"/>
-      <c r="Y9" s="64"/>
-      <c r="Z9" s="64"/>
-      <c r="AA9" s="64"/>
-      <c r="AB9" s="65"/>
-      <c r="AC9" s="88"/>
-      <c r="AD9" s="67"/>
-      <c r="AE9" s="67"/>
-      <c r="AF9" s="67"/>
-      <c r="AG9" s="67"/>
-      <c r="AH9" s="67"/>
-      <c r="AI9" s="67"/>
-      <c r="AJ9" s="67"/>
-      <c r="AK9" s="71"/>
-      <c r="AL9" s="82"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="27"/>
+      <c r="V9" s="27"/>
+      <c r="W9" s="27"/>
+      <c r="X9" s="27"/>
+      <c r="Y9" s="27"/>
+      <c r="Z9" s="27"/>
+      <c r="AA9" s="27"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="47"/>
+      <c r="AE9" s="47"/>
+      <c r="AF9" s="47"/>
+      <c r="AG9" s="47"/>
+      <c r="AH9" s="47"/>
+      <c r="AI9" s="47"/>
+      <c r="AJ9" s="47"/>
+      <c r="AK9" s="20"/>
+      <c r="AL9" s="22"/>
     </row>
     <row r="10" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="89"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="90"/>
-      <c r="J10" s="90"/>
-      <c r="K10" s="90"/>
-      <c r="L10" s="90"/>
-      <c r="M10" s="90"/>
-      <c r="N10" s="91"/>
-      <c r="O10" s="61"/>
-      <c r="P10" s="61"/>
-      <c r="Q10" s="61"/>
-      <c r="R10" s="62"/>
-      <c r="S10" s="64"/>
-      <c r="T10" s="64"/>
-      <c r="U10" s="64"/>
-      <c r="V10" s="64"/>
-      <c r="W10" s="64"/>
-      <c r="X10" s="64"/>
-      <c r="Y10" s="64"/>
-      <c r="Z10" s="64"/>
-      <c r="AA10" s="64"/>
-      <c r="AB10" s="65"/>
-      <c r="AC10" s="88"/>
-      <c r="AD10" s="67"/>
-      <c r="AE10" s="67"/>
-      <c r="AF10" s="67"/>
-      <c r="AG10" s="67"/>
-      <c r="AH10" s="67"/>
-      <c r="AI10" s="67"/>
-      <c r="AJ10" s="67"/>
-      <c r="AK10" s="71"/>
-      <c r="AL10" s="82"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="27"/>
+      <c r="X10" s="27"/>
+      <c r="Y10" s="27"/>
+      <c r="Z10" s="27"/>
+      <c r="AA10" s="27"/>
+      <c r="AB10" s="28"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="47"/>
+      <c r="AE10" s="47"/>
+      <c r="AF10" s="47"/>
+      <c r="AG10" s="47"/>
+      <c r="AH10" s="47"/>
+      <c r="AI10" s="47"/>
+      <c r="AJ10" s="47"/>
+      <c r="AK10" s="20"/>
+      <c r="AL10" s="22"/>
     </row>
     <row r="11" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="93"/>
-      <c r="J11" s="93"/>
-      <c r="K11" s="93"/>
-      <c r="L11" s="93"/>
-      <c r="M11" s="93"/>
-      <c r="N11" s="94"/>
-      <c r="O11" s="77"/>
-      <c r="P11" s="77"/>
-      <c r="Q11" s="77"/>
-      <c r="R11" s="78"/>
-      <c r="S11" s="80"/>
-      <c r="T11" s="80"/>
-      <c r="U11" s="80"/>
-      <c r="V11" s="80"/>
-      <c r="W11" s="80"/>
-      <c r="X11" s="80"/>
-      <c r="Y11" s="80"/>
-      <c r="Z11" s="80"/>
-      <c r="AA11" s="80"/>
-      <c r="AB11" s="81"/>
-      <c r="AC11" s="95" t="s">
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="88"/>
+      <c r="J11" s="88"/>
+      <c r="K11" s="88"/>
+      <c r="L11" s="88"/>
+      <c r="M11" s="88"/>
+      <c r="N11" s="89"/>
+      <c r="O11" s="45"/>
+      <c r="P11" s="45"/>
+      <c r="Q11" s="45"/>
+      <c r="R11" s="46"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
+      <c r="X11" s="30"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
+      <c r="AA11" s="30"/>
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="AD11" s="96"/>
-      <c r="AE11" s="96"/>
-      <c r="AF11" s="96"/>
-      <c r="AG11" s="96"/>
-      <c r="AH11" s="96"/>
-      <c r="AI11" s="96"/>
-      <c r="AJ11" s="96"/>
-      <c r="AK11" s="96"/>
-      <c r="AL11" s="97"/>
+      <c r="AD11" s="41"/>
+      <c r="AE11" s="41"/>
+      <c r="AF11" s="41"/>
+      <c r="AG11" s="41"/>
+      <c r="AH11" s="41"/>
+      <c r="AI11" s="41"/>
+      <c r="AJ11" s="41"/>
+      <c r="AK11" s="41"/>
+      <c r="AL11" s="42"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
@@ -1688,125 +1688,125 @@
     </row>
     <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="40"/>
-      <c r="R13" s="40"/>
-      <c r="S13" s="40"/>
-      <c r="T13" s="40"/>
-      <c r="U13" s="40"/>
-      <c r="V13" s="40"/>
-      <c r="W13" s="40"/>
-      <c r="X13" s="40"/>
-      <c r="Y13" s="40"/>
-      <c r="Z13" s="40"/>
-      <c r="AA13" s="40"/>
-      <c r="AB13" s="40"/>
-      <c r="AC13" s="40"/>
-      <c r="AD13" s="40"/>
-      <c r="AE13" s="40"/>
-      <c r="AF13" s="40"/>
-      <c r="AG13" s="40"/>
-      <c r="AH13" s="40"/>
-      <c r="AI13" s="40"/>
-      <c r="AJ13" s="40"/>
-      <c r="AK13" s="40"/>
-      <c r="AL13" s="40"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="65"/>
+      <c r="U13" s="65"/>
+      <c r="V13" s="65"/>
+      <c r="W13" s="65"/>
+      <c r="X13" s="65"/>
+      <c r="Y13" s="65"/>
+      <c r="Z13" s="65"/>
+      <c r="AA13" s="65"/>
+      <c r="AB13" s="65"/>
+      <c r="AC13" s="65"/>
+      <c r="AD13" s="65"/>
+      <c r="AE13" s="65"/>
+      <c r="AF13" s="65"/>
+      <c r="AG13" s="65"/>
+      <c r="AH13" s="65"/>
+      <c r="AI13" s="65"/>
+      <c r="AJ13" s="65"/>
+      <c r="AK13" s="65"/>
+      <c r="AL13" s="65"/>
     </row>
     <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="40"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="40"/>
-      <c r="R14" s="40"/>
-      <c r="S14" s="40"/>
-      <c r="T14" s="40"/>
-      <c r="U14" s="40"/>
-      <c r="V14" s="40"/>
-      <c r="W14" s="40"/>
-      <c r="X14" s="40"/>
-      <c r="Y14" s="40"/>
-      <c r="Z14" s="40"/>
-      <c r="AA14" s="40"/>
-      <c r="AB14" s="40"/>
-      <c r="AC14" s="40"/>
-      <c r="AD14" s="40"/>
-      <c r="AE14" s="40"/>
-      <c r="AF14" s="40"/>
-      <c r="AG14" s="40"/>
-      <c r="AH14" s="40"/>
-      <c r="AI14" s="40"/>
-      <c r="AJ14" s="40"/>
-      <c r="AK14" s="40"/>
-      <c r="AL14" s="40"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="65"/>
+      <c r="P14" s="65"/>
+      <c r="Q14" s="65"/>
+      <c r="R14" s="65"/>
+      <c r="S14" s="65"/>
+      <c r="T14" s="65"/>
+      <c r="U14" s="65"/>
+      <c r="V14" s="65"/>
+      <c r="W14" s="65"/>
+      <c r="X14" s="65"/>
+      <c r="Y14" s="65"/>
+      <c r="Z14" s="65"/>
+      <c r="AA14" s="65"/>
+      <c r="AB14" s="65"/>
+      <c r="AC14" s="65"/>
+      <c r="AD14" s="65"/>
+      <c r="AE14" s="65"/>
+      <c r="AF14" s="65"/>
+      <c r="AG14" s="65"/>
+      <c r="AH14" s="65"/>
+      <c r="AI14" s="65"/>
+      <c r="AJ14" s="65"/>
+      <c r="AK14" s="65"/>
+      <c r="AL14" s="65"/>
     </row>
     <row r="15" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
-      <c r="U15" s="34"/>
-      <c r="V15" s="34"/>
-      <c r="W15" s="34"/>
-      <c r="X15" s="34"/>
-      <c r="Y15" s="34"/>
-      <c r="Z15" s="34"/>
-      <c r="AA15" s="34"/>
-      <c r="AB15" s="34"/>
-      <c r="AC15" s="34"/>
-      <c r="AD15" s="34"/>
-      <c r="AE15" s="34"/>
-      <c r="AF15" s="34"/>
-      <c r="AG15" s="34"/>
-      <c r="AH15" s="34"/>
-      <c r="AI15" s="34"/>
-      <c r="AJ15" s="34"/>
-      <c r="AK15" s="34"/>
-      <c r="AL15" s="34"/>
+      <c r="B15" s="84"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="84"/>
+      <c r="P15" s="84"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84"/>
+      <c r="S15" s="84"/>
+      <c r="T15" s="84"/>
+      <c r="U15" s="84"/>
+      <c r="V15" s="84"/>
+      <c r="W15" s="84"/>
+      <c r="X15" s="84"/>
+      <c r="Y15" s="84"/>
+      <c r="Z15" s="84"/>
+      <c r="AA15" s="84"/>
+      <c r="AB15" s="84"/>
+      <c r="AC15" s="84"/>
+      <c r="AD15" s="84"/>
+      <c r="AE15" s="84"/>
+      <c r="AF15" s="84"/>
+      <c r="AG15" s="84"/>
+      <c r="AH15" s="84"/>
+      <c r="AI15" s="84"/>
+      <c r="AJ15" s="84"/>
+      <c r="AK15" s="84"/>
+      <c r="AL15" s="84"/>
     </row>
     <row r="16" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
@@ -1850,47 +1850,47 @@
     </row>
     <row r="17" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="42" t="s">
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
-      <c r="U17" s="42"/>
-      <c r="V17" s="42"/>
-      <c r="W17" s="42"/>
-      <c r="X17" s="42"/>
-      <c r="Y17" s="42"/>
-      <c r="Z17" s="42"/>
-      <c r="AA17" s="42"/>
-      <c r="AB17" s="42"/>
-      <c r="AC17" s="42"/>
-      <c r="AD17" s="42"/>
-      <c r="AE17" s="42"/>
-      <c r="AF17" s="42"/>
-      <c r="AG17" s="42"/>
-      <c r="AH17" s="42"/>
-      <c r="AI17" s="42"/>
-      <c r="AJ17" s="42"/>
-      <c r="AK17" s="42"/>
-      <c r="AL17" s="42"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="35"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="35"/>
+      <c r="X17" s="35"/>
+      <c r="Y17" s="35"/>
+      <c r="Z17" s="35"/>
+      <c r="AA17" s="35"/>
+      <c r="AB17" s="35"/>
+      <c r="AC17" s="35"/>
+      <c r="AD17" s="35"/>
+      <c r="AE17" s="35"/>
+      <c r="AF17" s="35"/>
+      <c r="AG17" s="35"/>
+      <c r="AH17" s="35"/>
+      <c r="AI17" s="35"/>
+      <c r="AJ17" s="35"/>
+      <c r="AK17" s="35"/>
+      <c r="AL17" s="35"/>
     </row>
     <row r="18" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
@@ -1934,47 +1934,47 @@
     </row>
     <row r="19" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="42" t="s">
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
-      <c r="U19" s="42"/>
-      <c r="V19" s="42"/>
-      <c r="W19" s="42"/>
-      <c r="X19" s="42"/>
-      <c r="Y19" s="42"/>
-      <c r="Z19" s="42"/>
-      <c r="AA19" s="42"/>
-      <c r="AB19" s="42"/>
-      <c r="AC19" s="42"/>
-      <c r="AD19" s="42"/>
-      <c r="AE19" s="42"/>
-      <c r="AF19" s="42"/>
-      <c r="AG19" s="42"/>
-      <c r="AH19" s="42"/>
-      <c r="AI19" s="42"/>
-      <c r="AJ19" s="42"/>
-      <c r="AK19" s="42"/>
-      <c r="AL19" s="42"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="35"/>
+      <c r="X19" s="35"/>
+      <c r="Y19" s="35"/>
+      <c r="Z19" s="35"/>
+      <c r="AA19" s="35"/>
+      <c r="AB19" s="35"/>
+      <c r="AC19" s="35"/>
+      <c r="AD19" s="35"/>
+      <c r="AE19" s="35"/>
+      <c r="AF19" s="35"/>
+      <c r="AG19" s="35"/>
+      <c r="AH19" s="35"/>
+      <c r="AI19" s="35"/>
+      <c r="AJ19" s="35"/>
+      <c r="AK19" s="35"/>
+      <c r="AL19" s="35"/>
     </row>
     <row r="20" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -2018,160 +2018,160 @@
     </row>
     <row r="21" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="18"/>
-      <c r="D21" s="17" t="s">
+      <c r="C21" s="78"/>
+      <c r="D21" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
-      <c r="M21" s="18"/>
-      <c r="N21" s="18"/>
-      <c r="O21" s="18"/>
-      <c r="P21" s="18"/>
-      <c r="Q21" s="18"/>
-      <c r="R21" s="18"/>
-      <c r="S21" s="17" t="s">
+      <c r="E21" s="78"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="78"/>
+      <c r="L21" s="78"/>
+      <c r="M21" s="78"/>
+      <c r="N21" s="78"/>
+      <c r="O21" s="78"/>
+      <c r="P21" s="78"/>
+      <c r="Q21" s="78"/>
+      <c r="R21" s="78"/>
+      <c r="S21" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="T21" s="18"/>
-      <c r="U21" s="18"/>
-      <c r="V21" s="18"/>
-      <c r="W21" s="17" t="s">
+      <c r="T21" s="78"/>
+      <c r="U21" s="78"/>
+      <c r="V21" s="78"/>
+      <c r="W21" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="X21" s="18"/>
-      <c r="Y21" s="18"/>
-      <c r="Z21" s="19" t="s">
+      <c r="X21" s="78"/>
+      <c r="Y21" s="78"/>
+      <c r="Z21" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="20"/>
-      <c r="AD21" s="20"/>
-      <c r="AE21" s="21"/>
-      <c r="AF21" s="31" t="s">
+      <c r="AA21" s="93"/>
+      <c r="AB21" s="93"/>
+      <c r="AC21" s="93"/>
+      <c r="AD21" s="93"/>
+      <c r="AE21" s="94"/>
+      <c r="AF21" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="AG21" s="18"/>
-      <c r="AH21" s="18"/>
-      <c r="AI21" s="18"/>
-      <c r="AJ21" s="18"/>
-      <c r="AK21" s="32"/>
+      <c r="AG21" s="78"/>
+      <c r="AH21" s="78"/>
+      <c r="AI21" s="78"/>
+      <c r="AJ21" s="78"/>
+      <c r="AK21" s="82"/>
       <c r="AL21" s="1"/>
     </row>
     <row r="22" spans="1:38" ht="52.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" s="14">
+      <c r="B22" s="63">
         <v>1</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="35" t="s">
+      <c r="C22" s="64"/>
+      <c r="D22" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="15"/>
-      <c r="S22" s="28">
+      <c r="E22" s="64"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="64"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="64"/>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="64"/>
+      <c r="R22" s="64"/>
+      <c r="S22" s="79">
         <v>1</v>
       </c>
-      <c r="T22" s="15"/>
-      <c r="U22" s="15"/>
-      <c r="V22" s="15"/>
-      <c r="W22" s="16" t="s">
+      <c r="T22" s="64"/>
+      <c r="U22" s="64"/>
+      <c r="V22" s="64"/>
+      <c r="W22" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="X22" s="15"/>
-      <c r="Y22" s="15"/>
-      <c r="Z22" s="22" t="s">
+      <c r="X22" s="64"/>
+      <c r="Y22" s="64"/>
+      <c r="Z22" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="AA22" s="23"/>
-      <c r="AB22" s="23"/>
-      <c r="AC22" s="23"/>
-      <c r="AD22" s="23"/>
-      <c r="AE22" s="24"/>
-      <c r="AF22" s="29" t="e">
+      <c r="AA22" s="96"/>
+      <c r="AB22" s="96"/>
+      <c r="AC22" s="96"/>
+      <c r="AD22" s="96"/>
+      <c r="AE22" s="97"/>
+      <c r="AF22" s="66" t="e">
         <f>S22*Z22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG22" s="15"/>
-      <c r="AH22" s="15"/>
-      <c r="AI22" s="15"/>
-      <c r="AJ22" s="15"/>
-      <c r="AK22" s="30"/>
+      <c r="AG22" s="64"/>
+      <c r="AH22" s="64"/>
+      <c r="AI22" s="64"/>
+      <c r="AJ22" s="64"/>
+      <c r="AK22" s="67"/>
       <c r="AL22" s="3"/>
     </row>
     <row r="23" spans="1:38" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-      <c r="B23" s="14">
+      <c r="B23" s="63">
         <v>2</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="35" t="s">
+      <c r="C23" s="64"/>
+      <c r="D23" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="28">
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="64"/>
+      <c r="K23" s="64"/>
+      <c r="L23" s="64"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="64"/>
+      <c r="P23" s="64"/>
+      <c r="Q23" s="64"/>
+      <c r="R23" s="64"/>
+      <c r="S23" s="79">
         <v>1</v>
       </c>
-      <c r="T23" s="15"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="15"/>
-      <c r="W23" s="16" t="s">
+      <c r="T23" s="64"/>
+      <c r="U23" s="64"/>
+      <c r="V23" s="64"/>
+      <c r="W23" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="15"/>
-      <c r="Z23" s="43" t="s">
+      <c r="X23" s="64"/>
+      <c r="Y23" s="64"/>
+      <c r="Z23" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="AA23" s="44"/>
-      <c r="AB23" s="44"/>
-      <c r="AC23" s="44"/>
-      <c r="AD23" s="44"/>
-      <c r="AE23" s="45"/>
-      <c r="AF23" s="29" t="e">
+      <c r="AA23" s="75"/>
+      <c r="AB23" s="75"/>
+      <c r="AC23" s="75"/>
+      <c r="AD23" s="75"/>
+      <c r="AE23" s="76"/>
+      <c r="AF23" s="66" t="e">
         <f>S23*Z23</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG23" s="15"/>
-      <c r="AH23" s="15"/>
-      <c r="AI23" s="15"/>
-      <c r="AJ23" s="15"/>
-      <c r="AK23" s="30"/>
+      <c r="AG23" s="64"/>
+      <c r="AH23" s="64"/>
+      <c r="AI23" s="64"/>
+      <c r="AJ23" s="64"/>
+      <c r="AK23" s="67"/>
       <c r="AL23" s="3"/>
     </row>
     <row r="24" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2248,15 +2248,15 @@
       <c r="AE25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="AF25" s="37" t="e">
+      <c r="AF25" s="72" t="e">
         <f>SUM(AF22:AK23)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG25" s="38"/>
-      <c r="AH25" s="38"/>
-      <c r="AI25" s="38"/>
-      <c r="AJ25" s="38"/>
-      <c r="AK25" s="38"/>
+      <c r="AG25" s="36"/>
+      <c r="AH25" s="36"/>
+      <c r="AI25" s="36"/>
+      <c r="AJ25" s="36"/>
+      <c r="AK25" s="36"/>
       <c r="AL25" s="1"/>
     </row>
     <row r="26" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2293,14 +2293,14 @@
       <c r="AE26" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="AF26" s="37" t="s">
+      <c r="AF26" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="AG26" s="38"/>
-      <c r="AH26" s="38"/>
-      <c r="AI26" s="38"/>
-      <c r="AJ26" s="38"/>
-      <c r="AK26" s="38"/>
+      <c r="AG26" s="36"/>
+      <c r="AH26" s="36"/>
+      <c r="AI26" s="36"/>
+      <c r="AJ26" s="36"/>
+      <c r="AK26" s="36"/>
       <c r="AL26" s="1"/>
     </row>
     <row r="27" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2337,98 +2337,98 @@
       <c r="AE27" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="AF27" s="37" t="e">
+      <c r="AF27" s="72" t="e">
         <f>SUM(AF25:AK26)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG27" s="38"/>
-      <c r="AH27" s="38"/>
-      <c r="AI27" s="38"/>
-      <c r="AJ27" s="38"/>
-      <c r="AK27" s="38"/>
+      <c r="AG27" s="36"/>
+      <c r="AH27" s="36"/>
+      <c r="AI27" s="36"/>
+      <c r="AJ27" s="36"/>
+      <c r="AK27" s="36"/>
       <c r="AL27" s="1"/>
     </row>
     <row r="28" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="33" t="s">
+      <c r="B28" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="33"/>
-      <c r="S28" s="33"/>
-      <c r="T28" s="33"/>
-      <c r="U28" s="33"/>
-      <c r="V28" s="33"/>
-      <c r="W28" s="33"/>
-      <c r="X28" s="33"/>
-      <c r="Y28" s="33"/>
-      <c r="Z28" s="33"/>
-      <c r="AA28" s="33"/>
-      <c r="AB28" s="33"/>
-      <c r="AC28" s="33"/>
-      <c r="AD28" s="33"/>
-      <c r="AE28" s="33"/>
-      <c r="AF28" s="33"/>
-      <c r="AG28" s="33"/>
-      <c r="AH28" s="33"/>
-      <c r="AI28" s="33"/>
-      <c r="AJ28" s="33"/>
-      <c r="AK28" s="33"/>
-      <c r="AL28" s="33"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83"/>
+      <c r="M28" s="83"/>
+      <c r="N28" s="83"/>
+      <c r="O28" s="83"/>
+      <c r="P28" s="83"/>
+      <c r="Q28" s="83"/>
+      <c r="R28" s="83"/>
+      <c r="S28" s="83"/>
+      <c r="T28" s="83"/>
+      <c r="U28" s="83"/>
+      <c r="V28" s="83"/>
+      <c r="W28" s="83"/>
+      <c r="X28" s="83"/>
+      <c r="Y28" s="83"/>
+      <c r="Z28" s="83"/>
+      <c r="AA28" s="83"/>
+      <c r="AB28" s="83"/>
+      <c r="AC28" s="83"/>
+      <c r="AD28" s="83"/>
+      <c r="AE28" s="83"/>
+      <c r="AF28" s="83"/>
+      <c r="AG28" s="83"/>
+      <c r="AH28" s="83"/>
+      <c r="AI28" s="83"/>
+      <c r="AJ28" s="83"/>
+      <c r="AK28" s="83"/>
+      <c r="AL28" s="83"/>
     </row>
     <row r="29" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3"/>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="41"/>
-      <c r="M29" s="41"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="41"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="41"/>
-      <c r="S29" s="41"/>
-      <c r="T29" s="41"/>
-      <c r="U29" s="41"/>
-      <c r="V29" s="41"/>
-      <c r="W29" s="41"/>
-      <c r="X29" s="41"/>
-      <c r="Y29" s="41"/>
-      <c r="Z29" s="41"/>
-      <c r="AA29" s="41"/>
-      <c r="AB29" s="41"/>
-      <c r="AC29" s="41"/>
-      <c r="AD29" s="41"/>
-      <c r="AE29" s="41"/>
-      <c r="AF29" s="41"/>
-      <c r="AG29" s="41"/>
-      <c r="AH29" s="41"/>
-      <c r="AI29" s="41"/>
-      <c r="AJ29" s="41"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="68"/>
+      <c r="M29" s="68"/>
+      <c r="N29" s="68"/>
+      <c r="O29" s="68"/>
+      <c r="P29" s="68"/>
+      <c r="Q29" s="68"/>
+      <c r="R29" s="68"/>
+      <c r="S29" s="68"/>
+      <c r="T29" s="68"/>
+      <c r="U29" s="68"/>
+      <c r="V29" s="68"/>
+      <c r="W29" s="68"/>
+      <c r="X29" s="68"/>
+      <c r="Y29" s="68"/>
+      <c r="Z29" s="68"/>
+      <c r="AA29" s="68"/>
+      <c r="AB29" s="68"/>
+      <c r="AC29" s="68"/>
+      <c r="AD29" s="68"/>
+      <c r="AE29" s="68"/>
+      <c r="AF29" s="68"/>
+      <c r="AG29" s="68"/>
+      <c r="AH29" s="68"/>
+      <c r="AI29" s="68"/>
+      <c r="AJ29" s="68"/>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
@@ -2573,23 +2573,23 @@
       <c r="P33" s="12"/>
       <c r="Q33" s="12"/>
       <c r="R33" s="10"/>
-      <c r="S33" s="39" t="s">
+      <c r="S33" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="T33" s="39"/>
-      <c r="U33" s="39"/>
-      <c r="V33" s="39"/>
-      <c r="W33" s="39"/>
-      <c r="X33" s="39"/>
-      <c r="Y33" s="39"/>
-      <c r="Z33" s="39"/>
-      <c r="AA33" s="39"/>
-      <c r="AB33" s="39"/>
-      <c r="AC33" s="39"/>
-      <c r="AD33" s="39"/>
-      <c r="AE33" s="39"/>
-      <c r="AF33" s="39"/>
-      <c r="AG33" s="39"/>
+      <c r="T33" s="62"/>
+      <c r="U33" s="62"/>
+      <c r="V33" s="62"/>
+      <c r="W33" s="62"/>
+      <c r="X33" s="62"/>
+      <c r="Y33" s="62"/>
+      <c r="Z33" s="62"/>
+      <c r="AA33" s="62"/>
+      <c r="AB33" s="62"/>
+      <c r="AC33" s="62"/>
+      <c r="AD33" s="62"/>
+      <c r="AE33" s="62"/>
+      <c r="AF33" s="62"/>
+      <c r="AG33" s="62"/>
       <c r="AH33" s="10"/>
       <c r="AI33" s="10"/>
       <c r="AJ33" s="10"/>
@@ -2606,34 +2606,34 @@
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
-      <c r="J34" s="25" t="s">
+      <c r="J34" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
-      <c r="P34" s="26"/>
-      <c r="Q34" s="26"/>
+      <c r="K34" s="71"/>
+      <c r="L34" s="71"/>
+      <c r="M34" s="71"/>
+      <c r="N34" s="71"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71"/>
       <c r="R34" s="10"/>
-      <c r="S34" s="27" t="s">
+      <c r="S34" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="T34" s="27"/>
-      <c r="U34" s="27"/>
-      <c r="V34" s="27"/>
-      <c r="W34" s="27"/>
-      <c r="X34" s="27"/>
-      <c r="Y34" s="27"/>
-      <c r="Z34" s="27"/>
-      <c r="AA34" s="27"/>
-      <c r="AB34" s="27"/>
-      <c r="AC34" s="27"/>
-      <c r="AD34" s="27"/>
-      <c r="AE34" s="27"/>
-      <c r="AF34" s="27"/>
-      <c r="AG34" s="27"/>
+      <c r="T34" s="69"/>
+      <c r="U34" s="69"/>
+      <c r="V34" s="69"/>
+      <c r="W34" s="69"/>
+      <c r="X34" s="69"/>
+      <c r="Y34" s="69"/>
+      <c r="Z34" s="69"/>
+      <c r="AA34" s="69"/>
+      <c r="AB34" s="69"/>
+      <c r="AC34" s="69"/>
+      <c r="AD34" s="69"/>
+      <c r="AE34" s="69"/>
+      <c r="AF34" s="69"/>
+      <c r="AG34" s="69"/>
       <c r="AH34" s="10"/>
       <c r="AI34" s="10"/>
       <c r="AJ34" s="10"/>
@@ -2701,21 +2701,21 @@
       <c r="P36" s="12"/>
       <c r="Q36" s="12"/>
       <c r="R36" s="10"/>
-      <c r="S36" s="39"/>
-      <c r="T36" s="39"/>
-      <c r="U36" s="39"/>
-      <c r="V36" s="39"/>
-      <c r="W36" s="39"/>
-      <c r="X36" s="39"/>
-      <c r="Y36" s="39"/>
-      <c r="Z36" s="39"/>
-      <c r="AA36" s="39"/>
-      <c r="AB36" s="39"/>
-      <c r="AC36" s="39"/>
-      <c r="AD36" s="39"/>
-      <c r="AE36" s="39"/>
-      <c r="AF36" s="39"/>
-      <c r="AG36" s="39"/>
+      <c r="S36" s="62"/>
+      <c r="T36" s="62"/>
+      <c r="U36" s="62"/>
+      <c r="V36" s="62"/>
+      <c r="W36" s="62"/>
+      <c r="X36" s="62"/>
+      <c r="Y36" s="62"/>
+      <c r="Z36" s="62"/>
+      <c r="AA36" s="62"/>
+      <c r="AB36" s="62"/>
+      <c r="AC36" s="62"/>
+      <c r="AD36" s="62"/>
+      <c r="AE36" s="62"/>
+      <c r="AF36" s="62"/>
+      <c r="AG36" s="62"/>
       <c r="AH36" s="10"/>
       <c r="AI36" s="10"/>
       <c r="AJ36" s="10"/>
@@ -2732,34 +2732,34 @@
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
-      <c r="J37" s="25" t="s">
+      <c r="J37" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="26"/>
+      <c r="K37" s="71"/>
+      <c r="L37" s="71"/>
+      <c r="M37" s="71"/>
+      <c r="N37" s="71"/>
+      <c r="O37" s="71"/>
+      <c r="P37" s="71"/>
+      <c r="Q37" s="71"/>
       <c r="R37" s="10"/>
-      <c r="S37" s="27" t="s">
+      <c r="S37" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-      <c r="W37" s="27"/>
-      <c r="X37" s="27"/>
-      <c r="Y37" s="27"/>
-      <c r="Z37" s="27"/>
-      <c r="AA37" s="27"/>
-      <c r="AB37" s="27"/>
-      <c r="AC37" s="27"/>
-      <c r="AD37" s="27"/>
-      <c r="AE37" s="27"/>
-      <c r="AF37" s="27"/>
-      <c r="AG37" s="27"/>
+      <c r="T37" s="69"/>
+      <c r="U37" s="69"/>
+      <c r="V37" s="69"/>
+      <c r="W37" s="69"/>
+      <c r="X37" s="69"/>
+      <c r="Y37" s="69"/>
+      <c r="Z37" s="69"/>
+      <c r="AA37" s="69"/>
+      <c r="AB37" s="69"/>
+      <c r="AC37" s="69"/>
+      <c r="AD37" s="69"/>
+      <c r="AE37" s="69"/>
+      <c r="AF37" s="69"/>
+      <c r="AG37" s="69"/>
       <c r="AH37" s="10"/>
       <c r="AI37" s="10"/>
       <c r="AJ37" s="10"/>
@@ -41170,18 +41170,28 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="S4:AB6"/>
-    <mergeCell ref="S2:AB3"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B8:N10"/>
-    <mergeCell ref="AC11:AL11"/>
-    <mergeCell ref="O7:R11"/>
-    <mergeCell ref="AD3:AJ10"/>
-    <mergeCell ref="S7:AB11"/>
-    <mergeCell ref="B6:N6"/>
-    <mergeCell ref="B2:N5"/>
-    <mergeCell ref="O2:R3"/>
-    <mergeCell ref="O4:R6"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="W23:Y23"/>
+    <mergeCell ref="D21:R21"/>
+    <mergeCell ref="Z21:AE21"/>
+    <mergeCell ref="S21:V21"/>
+    <mergeCell ref="Z22:AE22"/>
+    <mergeCell ref="J37:Q37"/>
+    <mergeCell ref="S37:AG37"/>
+    <mergeCell ref="S23:V23"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="S22:V22"/>
+    <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="AF21:AK21"/>
+    <mergeCell ref="B28:AL28"/>
+    <mergeCell ref="B15:AL15"/>
+    <mergeCell ref="D23:R23"/>
+    <mergeCell ref="W22:Y22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="AF26:AK26"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B11:N11"/>
+    <mergeCell ref="K7:N7"/>
     <mergeCell ref="S36:AG36"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B13:AL14"/>
@@ -41198,28 +41208,18 @@
     <mergeCell ref="Z23:AE23"/>
     <mergeCell ref="G17:AL17"/>
     <mergeCell ref="W21:Y21"/>
-    <mergeCell ref="J37:Q37"/>
-    <mergeCell ref="S37:AG37"/>
-    <mergeCell ref="S23:V23"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="S22:V22"/>
-    <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="AF21:AK21"/>
-    <mergeCell ref="B28:AL28"/>
-    <mergeCell ref="B15:AL15"/>
-    <mergeCell ref="D23:R23"/>
-    <mergeCell ref="W22:Y22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="AF26:AK26"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B11:N11"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="W23:Y23"/>
-    <mergeCell ref="D21:R21"/>
-    <mergeCell ref="Z21:AE21"/>
-    <mergeCell ref="S21:V21"/>
-    <mergeCell ref="Z22:AE22"/>
+    <mergeCell ref="S4:AB6"/>
+    <mergeCell ref="S2:AB3"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B8:N10"/>
+    <mergeCell ref="AC11:AL11"/>
+    <mergeCell ref="O7:R11"/>
+    <mergeCell ref="AD3:AJ10"/>
+    <mergeCell ref="S7:AB11"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="B2:N5"/>
+    <mergeCell ref="O2:R3"/>
+    <mergeCell ref="O4:R6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="97" orientation="portrait" r:id="rId1"/>
